--- a/Error Code Guide - UNI-300VA Labeler.xlsx
+++ b/Error Code Guide - UNI-300VA Labeler.xlsx
@@ -614,12 +614,113 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>1. Stop the line and pull the rejected bottles
-2. Look at the rejects: label straight? code clear and correct?
-3. Check the label roll is the right item # for this batch
-4. Fix what you found (see the matching error below)
-5. Reset the error and restart the line
-6. Watch the next bottles and tell your lead</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Stop the line and pull the rejected bottles</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+2. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Look at the rejects: label straight? code clear and correct?</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+3. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Check the label roll is the right item # for this batch</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+4. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Fix what you found (see the matching error below)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+5. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Reset the error and restart the line</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+6. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Watch the next bottles and tell your lead</t>
+          </r>
         </is>
       </c>
     </row>
@@ -656,11 +757,95 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>1. Pull the affected bottles and set them aside for QA
-2. Check the code on the label matches the batch record
-3. Check the coder ribbon (see ribbon errors)
-4. Reset the error and restart the line
-5. Tell your lead / QA</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Pull the affected bottles and set them aside for QA</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+2. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Check the code on the label matches the batch record</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+3. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Check the coder ribbon (see ribbon errors)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+4. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Reset the error and restart the line</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+5. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Tell your lead / QA</t>
+          </r>
         </is>
       </c>
     </row>
@@ -697,10 +882,77 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>1. Pull the unlabeled bottles
-2. Check the label roll and that the web follows the threading diagram
-3. Remove any stuck or folded labels
-4. Reset the error and restart the line</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Pull the unlabeled bottles</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+2. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Check the label roll and that the web follows the threading diagram</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+3. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Remove any stuck or folded labels</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+4. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Reset the error and restart the line</t>
+          </r>
         </is>
       </c>
     </row>
@@ -735,10 +987,77 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>1. Get the next roll ready
-2. Check the item # and lot match the batch record
-3. Change the roll when it runs out
-4. Record the roll change</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Get the next roll ready</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+2. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Check the item # and lot match the batch record</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+3. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Change the roll when it runs out</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+4. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Record the roll change</t>
+          </r>
         </is>
       </c>
     </row>
@@ -773,12 +1092,113 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>1. Stop the line
-2. Load the new roll (check item # and lot)
-3. Thread the web using the diagram on the machine
-4. Record the roll change
-5. Reset the error and restart the line
-6. Check the first labeled bottles</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Stop the line</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+2. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Load the new roll (check item # and lot)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+3. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Thread the web using the diagram on the machine</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+4. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Record the roll change</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+5. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Reset the error and restart the line</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+6. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Check the first labeled bottles</t>
+          </r>
         </is>
       </c>
     </row>
@@ -815,11 +1235,95 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>1. Stop the line
-2. Remove the torn liner
-3. Re-thread the web using the diagram on the machine
-4. Reset the error and restart the line
-5. Check the first labeled bottles</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Stop the line</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+2. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Remove the torn liner</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+3. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Re-thread the web using the diagram on the machine</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+4. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Reset the error and restart the line</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+5. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Check the first labeled bottles</t>
+          </r>
         </is>
       </c>
     </row>
@@ -854,12 +1358,113 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>1. Stop the line
-2. Open the coder cassette and replace the ribbon
-3. Follow the threading diagram inside the cassette
-4. Close and lock the cassette
-5. Check the screen shows RUNNING
-6. Restart the line and check the first codes</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Stop the line</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+2. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Open the coder cassette and replace the ribbon</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+3. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Follow the threading diagram inside the cassette</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+4. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Close and lock the cassette</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+5. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Check the screen shows RUNNING</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+6. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Restart the line and check the first codes</t>
+          </r>
         </is>
       </c>
     </row>
@@ -896,11 +1501,95 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>1. Stop the line
-2. Open the cassette and re-thread or replace the ribbon
-3. Close and lock the cassette
-4. Clear the message on the coder screen
-5. Restart the line and check the first codes</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Stop the line</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+2. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Open the cassette and re-thread or replace the ribbon</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+3. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Close and lock the cassette</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+4. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Clear the message on the coder screen</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+5. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Restart the line and check the first codes</t>
+          </r>
         </is>
       </c>
     </row>
@@ -937,10 +1626,77 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>1. Check the message on the Videojet screen and clear it
-2. Make sure the correct job is selected and matches the batch record
-3. Press start - the screen should show green RUNNING
-4. Restart the line and check the first codes</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Check the message on the Videojet screen and clear it</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+2. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Make sure the correct job is selected and matches the batch record</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+3. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Press start - the screen should show green RUNNING</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+4. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Restart the line and check the first codes</t>
+          </r>
         </is>
       </c>
     </row>
@@ -976,9 +1732,59 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>1. Stop the line before reaching in
-2. Remove the fallen or jammed bottles
-3. Reset the error and restart the line</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Stop the line before reaching in</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+2. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Remove the fallen or jammed bottles</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+3. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Reset the error and restart the line</t>
+          </r>
         </is>
       </c>
     </row>
@@ -1014,9 +1820,59 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>1. Stop the line
-2. Remove the stuck bottle at the indexing wheel
-3. Reset the error and restart the line</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Stop the line</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+2. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Remove the stuck bottle at the indexing wheel</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+3. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Reset the error and restart the line</t>
+          </r>
         </is>
       </c>
     </row>
@@ -1051,8 +1907,41 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>1. Empty the reject bin and keep rejects separate
-2. Reset the error and restart the line</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Empty the reject bin and keep rejects separate</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+2. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Reset the error and restart the line</t>
+          </r>
         </is>
       </c>
     </row>
@@ -1087,8 +1976,41 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>1. Close all guard doors until they latch
-2. Reset the error and restart the line</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Close all guard doors until they latch</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+2. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Reset the error and restart the line</t>
+          </r>
         </is>
       </c>
     </row>
@@ -1123,9 +2045,59 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>1. Make sure the area is safe and everyone is clear
-2. Twist or pull the E-stop button to release it
-3. Reset the error and restart the line</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">1. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Make sure the area is safe and everyone is clear</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+2. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Twist or pull the E-stop button to release it</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+3. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Reset the error and restart the line</t>
+          </r>
         </is>
       </c>
     </row>

--- a/Error Code Guide - UNI-300VA Labeler.xlsx
+++ b/Error Code Guide - UNI-300VA Labeler.xlsx
@@ -607,9 +607,59 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>• Labels crooked or wrinkled
-• Lot / exp code missing, faded or wrong
-• Wrong label roll loaded</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">• </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Labels crooked or wrinkled</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+• </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Lot / exp code missing, faded or wrong</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+• </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Wrong label roll loaded</t>
+          </r>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -750,9 +800,59 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>• Lot / exp code missing or faded
-• Ribbon wrinkled or running out
-• Wrong code loaded on the coder</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">• </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Lot / exp code missing or faded</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+• </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Ribbon wrinkled or running out</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+• </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Wrong code loaded on the coder</t>
+          </r>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -875,9 +975,59 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>• Labeler ran out of labels
-• Labels stuck to each other or to the liner
-• Label web not threaded right</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">• </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Labeler ran out of labels</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+• </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Labels stuck to each other or to the liner</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+• </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Label web not threaded right</t>
+          </r>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -982,7 +1132,23 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>• Label roll is almost empty</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">• </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Label roll is almost empty</t>
+          </r>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -1087,7 +1253,23 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>• Label roll is empty</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">• </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Label roll is empty</t>
+          </r>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -1228,9 +1410,59 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>• Label liner torn
-• Liner caught on a guide
-• Bad splice in the roll</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">• </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Label liner torn</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+• </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Liner caught on a guide</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+• </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Bad splice in the roll</t>
+          </r>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -1353,7 +1585,23 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>• Coder ribbon almost used up or empty</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">• </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Coder ribbon almost used up or empty</t>
+          </r>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1494,9 +1742,59 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>• Ribbon torn or slipped off
-• Ribbon threaded wrong
-• Cassette not locked</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">• </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Ribbon torn or slipped off</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+• </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Ribbon threaded wrong</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+• </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Cassette not locked</t>
+          </r>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -1619,9 +1917,59 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>• Coder is stopped or paused
-• Cassette open or message not cleared
-• No job (code) selected</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">• </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Coder is stopped or paused</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+• </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Cassette open or message not cleared</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+• </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>No job (code) selected</t>
+          </r>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1726,8 +2074,41 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>• Bottle fell over or got stuck
-• Damaged or wrong bottles on the line</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">• </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Bottle fell over or got stuck</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+• </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Damaged or wrong bottles on the line</t>
+          </r>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1814,8 +2195,41 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>• Bottle stuck at the indexing wheel
-• Bottles crowded at the infeed</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">• </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Bottle stuck at the indexing wheel</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">
+• </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Bottles crowded at the infeed</t>
+          </r>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1902,7 +2316,23 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>• Reject bin is full</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">• </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Reject bin is full</t>
+          </r>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -1971,7 +2401,23 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>• A guard door is open or not fully closed</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">• </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>A guard door is open or not fully closed</t>
+          </r>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -2040,7 +2486,23 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>• Someone pressed the red E-stop button</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <b val="1"/>
+              <color rgb="001F3A4D"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">• </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Aptos Narrow"/>
+              <color rgb="00222222"/>
+              <sz val="13"/>
+            </rPr>
+            <t>Someone pressed the red E-stop button</t>
+          </r>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">

--- a/Error Code Guide - UNI-300VA Labeler.xlsx
+++ b/Error Code Guide - UNI-300VA Labeler.xlsx
@@ -2291,7 +2291,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>13000</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="666750" cy="762000"/>
+    <xdr:ext cx="762000" cy="676275"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Picture 1">

--- a/Error Code Guide - UNI-300VA Labeler.xlsx
+++ b/Error Code Guide - UNI-300VA Labeler.xlsx
@@ -2291,7 +2291,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>13000</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="762000" cy="676275"/>
+    <xdr:ext cx="666750" cy="762000"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Picture 1">

--- a/Error Code Guide - UNI-300VA Labeler.xlsx
+++ b/Error Code Guide - UNI-300VA Labeler.xlsx
@@ -7,16 +7,40 @@
     <sheet sheetId="1" name="Error Codes" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Error Codes'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Error Codes'!$6:$6</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
-  <si>
-    <t>UNI-300VA LABELER ERROR CODE GUIDE</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFF6B53B"/>
+        <sz val="11"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>OPERATOR'S TROUBLESHOOTING GUIDE</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+        <sz val="26"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">
+UNI-300VA LABELER</t>
+    </r>
+  </si>
+  <si>
+    <t>Find the alarm on the machine screen, then follow the steps in order.</t>
+  </si>
+  <si>
+    <t>Updated Oct 19, 2026</t>
   </si>
   <si>
     <t>ERROR CODE</t>
@@ -2147,7 +2171,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -2156,9 +2180,14 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="20"/>
+      <color rgb="FF1F3A4D"/>
+      <sz val="10.5"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7B8C"/>
+      <sz val="10.5"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
@@ -2185,7 +2214,7 @@
       <name val="Aptos Narrow"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2194,12 +2223,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F3A4D"/>
+        <fgColor rgb="FFF6B53B"/>
       </patternFill>
     </fill>
     <fill>
+      <gradientFill degree="0">
+        <stop position="0">
+          <color rgb="FF1F3A4D"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FF2F5878"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6B53B"/>
+        <fgColor rgb="FFE9EFF5"/>
       </patternFill>
     </fill>
     <fill>
@@ -2213,12 +2252,21 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD0D7DE"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2236,33 +2284,65 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFF6B53B"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D7DE"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D7DE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D7DE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFC62828"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -2287,11 +2367,11 @@
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>28999</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>13000</xdr:rowOff>
+      <xdr:colOff>1657350</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="666750" cy="762000"/>
+    <xdr:ext cx="609600" cy="704850"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Picture 1">
@@ -2651,7 +2731,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -2660,224 +2740,245 @@
     <col min="4" max="4" width="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="1" ht="7" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
     </row>
-    <row r="2" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
+    <row r="2" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="3"/>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="3" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="2" t="s">
+    </row>
+    <row r="5" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="B6" s="6" t="s">
         <v>4</v>
       </c>
+      <c r="C6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="5" ht="265" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="4" t="s">
+    <row r="7" ht="265" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="5"/>
+      <c r="B7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="9"/>
     </row>
-    <row r="6" ht="197" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="7" t="s">
+    <row r="8" ht="197" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="8"/>
+      <c r="B8" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="12"/>
     </row>
-    <row r="7" ht="163" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="4" t="s">
+    <row r="9" ht="163" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="5"/>
+      <c r="B9" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="9"/>
     </row>
-    <row r="8" ht="112" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="7" t="s">
+    <row r="10" ht="112" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="8"/>
+      <c r="B10" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="12"/>
     </row>
-    <row r="9" ht="95" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="4" t="s">
+    <row r="11" ht="95" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="5"/>
+      <c r="B11" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="9"/>
     </row>
-    <row r="10" ht="163" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="7" t="s">
+    <row r="12" ht="163" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="8"/>
-    </row>
-    <row r="11" ht="129" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="B12" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C12" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="5"/>
-    </row>
-    <row r="12" ht="197" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="8"/>
+      <c r="D12" s="12"/>
     </row>
     <row r="13" ht="129" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="9"/>
+    </row>
+    <row r="14" ht="197" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="C14" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="D14" s="12"/>
+    </row>
+    <row r="15" ht="129" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="5"/>
+      <c r="B15" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="9"/>
     </row>
-    <row r="14" ht="146" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="7" t="s">
+    <row r="16" ht="146" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="8"/>
-    </row>
-    <row r="15" ht="78" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="B16" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="C16" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="5"/>
-    </row>
-    <row r="16" ht="95" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" s="8"/>
+      <c r="D16" s="12"/>
     </row>
     <row r="17" ht="78" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="9"/>
+    </row>
+    <row r="18" ht="95" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="C18" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="D18" s="12"/>
+    </row>
+    <row r="19" ht="78" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="5"/>
+      <c r="B19" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="9"/>
     </row>
-    <row r="18" ht="61" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="7" t="s">
+    <row r="20" ht="61" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="8"/>
+      <c r="B20" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="12"/>
     </row>
-    <row r="19" ht="112" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="4" t="s">
+    <row r="21" ht="112" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D19" s="5"/>
-    </row>
-    <row r="21" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
+      <c r="B21" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
+      <c r="C21" s="8" t="s">
+        <v>51</v>
+      </c>
       <c r="D21" s="9"/>
     </row>
+    <row r="23" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="A21:D21"/>
+  <mergeCells count="4">
+    <mergeCell ref="A2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A23:D23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
